--- a/shared codes/data/데이터 명세.xlsx
+++ b/shared codes/data/데이터 명세.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/downy/Documents/2025 LG aimers/DKU-LG-Capstone-6/shared codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D835B4BE-CAC0-E048-83AC-5A0BF71F4152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64021AB-B4AE-7948-91D8-17A329256B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32320" yWindow="-28300" windowWidth="51200" windowHeight="28300" xr2:uid="{DA19DC8F-9B0C-4123-9D80-76730E032BF2}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{DA19DC8F-9B0C-4123-9D80-76730E032BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터 명세" sheetId="1" r:id="rId1"/>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>파트너 정자와 혼합된 난자의 수</t>
-  </si>
-  <si>
-    <t>기증자 정자와 혼합된 난자 수</t>
   </si>
   <si>
     <t>기증자 정자와 혼합된 난자의 수</t>
@@ -575,6 +572,10 @@
   </si>
   <si>
     <t>다훈</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>기증자 정자와 혼합된 난자 수</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1740,19 +1741,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1760,16 +1761,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F2" s="1"/>
     </row>
@@ -1778,10 +1779,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -1833,10 +1834,10 @@
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -1855,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -1891,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F9" s="12"/>
     </row>
@@ -1909,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F10" s="12"/>
     </row>
@@ -1927,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F11" s="12"/>
     </row>
@@ -1936,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>20</v>
@@ -1945,14 +1946,14 @@
         <v>1</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F12" s="18"/>
       <c r="I12" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="J12" s="21" t="s">
         <v>158</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1969,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F13" s="18"/>
     </row>
@@ -1987,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F14" s="20"/>
     </row>
@@ -2005,14 +2006,14 @@
         <v>1</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F15" s="20"/>
       <c r="I15" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="27" t="s">
         <v>160</v>
-      </c>
-      <c r="J15" s="27" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2029,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -2047,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -2065,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F18" s="1"/>
     </row>
@@ -2083,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F19" s="20"/>
     </row>
@@ -2101,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F20" s="18"/>
     </row>
@@ -2119,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F21" s="20"/>
     </row>
@@ -2137,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F22" s="20"/>
     </row>
@@ -2155,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" s="20"/>
     </row>
@@ -2173,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F24" s="20"/>
     </row>
@@ -2185,16 +2186,16 @@
         <v>45</v>
       </c>
       <c r="C25" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="17">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="18" t="s">
         <v>156</v>
-      </c>
-      <c r="D25" s="17">
-        <v>1</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2211,10 +2212,10 @@
         <v>1</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2231,10 +2232,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2251,10 +2252,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2265,16 +2266,16 @@
         <v>52</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D29" s="13">
         <v>1</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2291,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F30" s="12"/>
     </row>
@@ -2309,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F31" s="26"/>
     </row>
@@ -2327,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F32" s="26"/>
     </row>
@@ -2345,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F33" s="26"/>
     </row>
@@ -2363,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="26"/>
     </row>
@@ -2381,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="26"/>
     </row>
@@ -2399,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="26"/>
     </row>
@@ -2417,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F37" s="26"/>
     </row>
@@ -2435,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="26"/>
     </row>
@@ -2453,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="26"/>
     </row>
@@ -2670,10 +2671,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="D53" s="6">
         <v>0</v>
@@ -2686,16 +2687,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="F54" s="7"/>
     </row>
@@ -2704,16 +2705,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="F55" s="7"/>
     </row>
@@ -2722,16 +2723,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="D56" s="6">
         <v>1</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F56" s="7"/>
     </row>
@@ -2740,16 +2741,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="D57" s="6">
+        <v>1</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="D57" s="6">
-        <v>1</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="F57" s="7"/>
     </row>
@@ -2758,16 +2759,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="D58" s="6">
         <v>1</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F58" s="7"/>
     </row>
@@ -2776,16 +2777,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="D59" s="6">
         <v>1</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F59" s="7"/>
     </row>
@@ -2794,16 +2795,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="D60" s="6">
         <v>1</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F60" s="7"/>
     </row>
@@ -2812,16 +2813,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="D61" s="8">
         <v>1</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F61" s="9"/>
     </row>
@@ -2830,16 +2831,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D62" s="8">
         <v>1</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F62" s="9"/>
     </row>
@@ -2848,16 +2849,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D63" s="8">
         <v>1</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F63" s="9"/>
     </row>
@@ -2866,10 +2867,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="16" t="s">
         <v>120</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>121</v>
       </c>
       <c r="D64" s="15">
         <v>0</v>
@@ -2882,10 +2883,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="D65" s="15">
         <v>0</v>
@@ -2898,10 +2899,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="16" t="s">
         <v>124</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>125</v>
       </c>
       <c r="D66" s="15">
         <v>0</v>
@@ -2914,10 +2915,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="16" t="s">
         <v>126</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>127</v>
       </c>
       <c r="D67" s="15">
         <v>0</v>
@@ -2930,10 +2931,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="16" t="s">
         <v>128</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>129</v>
       </c>
       <c r="D68" s="15">
         <v>0</v>
@@ -2946,16 +2947,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F69" s="1"/>
     </row>

--- a/shared codes/data/데이터 명세.xlsx
+++ b/shared codes/data/데이터 명세.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/downy/Documents/2025 LG aimers/DKU-LG-Capstone-6/shared codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64021AB-B4AE-7948-91D8-17A329256B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320D0073-E7B0-EF41-885D-0233D3798AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{DA19DC8F-9B0C-4123-9D80-76730E032BF2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{DA19DC8F-9B0C-4123-9D80-76730E032BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터 명세" sheetId="1" r:id="rId1"/>

--- a/shared codes/data/데이터 명세.xlsx
+++ b/shared codes/data/데이터 명세.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/downy/Documents/2025 LG aimers/DKU-LG-Capstone-6/shared codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320D0073-E7B0-EF41-885D-0233D3798AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647C39C0-589E-B244-A46D-25517A3AE037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{DA19DC8F-9B0C-4123-9D80-76730E032BF2}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="165">
   <si>
     <t>번호</t>
   </si>
@@ -576,6 +576,18 @@
   </si>
   <si>
     <t>기증자 정자와 혼합된 난자 수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IVF 컬럼</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1000,7 +1012,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1130,6 +1142,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1259,7 +1282,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1343,6 +1366,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1725,15 +1751,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBA87C3D-28BB-48EC-B99F-1013E1304AD3}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="36.1640625" customWidth="1"/>
     <col min="3" max="3" width="77.33203125" customWidth="1"/>
     <col min="5" max="5" width="43.6640625" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="24.5" customWidth="1"/>
+    <col min="10" max="10" width="64.5" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2034,7 +2062,7 @@
       </c>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:13">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2052,7 +2080,7 @@
       </c>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2070,7 +2098,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:13">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -2088,7 +2116,7 @@
       </c>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:13">
       <c r="A20" s="17">
         <v>19</v>
       </c>
@@ -2106,7 +2134,7 @@
       </c>
       <c r="F20" s="18"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:13">
       <c r="A21" s="19">
         <v>20</v>
       </c>
@@ -2124,7 +2152,7 @@
       </c>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:13">
       <c r="A22" s="19">
         <v>21</v>
       </c>
@@ -2141,8 +2169,11 @@
         <v>131</v>
       </c>
       <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="M22" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="19">
         <v>22</v>
       </c>
@@ -2160,7 +2191,7 @@
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:13">
       <c r="A24" s="19">
         <v>23</v>
       </c>
@@ -2178,7 +2209,7 @@
       </c>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:13">
       <c r="A25" s="17">
         <v>24</v>
       </c>
@@ -2198,7 +2229,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:13">
       <c r="A26" s="23">
         <v>25</v>
       </c>
@@ -2218,7 +2249,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:13">
       <c r="A27" s="17">
         <v>26</v>
       </c>
@@ -2238,7 +2269,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:13">
       <c r="A28" s="17">
         <v>27</v>
       </c>
@@ -2257,8 +2288,11 @@
       <c r="F28" s="18" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="M28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -2277,8 +2311,26 @@
       <c r="F29" s="12" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="H29" s="13">
+        <v>8</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="M29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -2295,8 +2347,26 @@
         <v>134</v>
       </c>
       <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="H30" s="13">
+        <v>28</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="K30" s="13">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="M30" s="28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="25">
         <v>30</v>
       </c>
@@ -2313,8 +2383,24 @@
         <v>134</v>
       </c>
       <c r="F31" s="26"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="H31" s="25">
+        <v>39</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="K31" s="25">
+        <v>0</v>
+      </c>
+      <c r="L31" s="26"/>
+      <c r="M31" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="25">
         <v>31</v>
       </c>
@@ -2331,8 +2417,24 @@
         <v>134</v>
       </c>
       <c r="F32" s="26"/>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="H32" s="10">
+        <v>44</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0</v>
+      </c>
+      <c r="L32" s="11"/>
+      <c r="M32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="25">
         <v>32</v>
       </c>
@@ -2349,8 +2451,24 @@
         <v>134</v>
       </c>
       <c r="F33" s="26"/>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="H33" s="10">
+        <v>42</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11"/>
+      <c r="M33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="25">
         <v>33</v>
       </c>
@@ -2367,8 +2485,20 @@
         <v>134</v>
       </c>
       <c r="F34" s="26"/>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="H34" s="10">
+        <v>43</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K34" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="25">
         <v>34</v>
       </c>
@@ -2385,8 +2515,20 @@
         <v>134</v>
       </c>
       <c r="F35" s="26"/>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="H35" s="10">
+        <v>45</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="25">
         <v>35</v>
       </c>
@@ -2403,8 +2545,20 @@
         <v>134</v>
       </c>
       <c r="F36" s="26"/>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="H36" s="10">
+        <v>46</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="K36" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="25">
         <v>36</v>
       </c>
@@ -2421,8 +2575,23 @@
         <v>134</v>
       </c>
       <c r="F37" s="26"/>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="H37" s="6">
+        <v>57</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K37" s="6">
+        <v>1</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="25">
         <v>37</v>
       </c>
@@ -2439,8 +2608,23 @@
         <v>134</v>
       </c>
       <c r="F38" s="26"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="H38" s="6">
+        <v>58</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K38" s="6">
+        <v>1</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="25">
         <v>38</v>
       </c>
@@ -2457,8 +2641,23 @@
         <v>134</v>
       </c>
       <c r="F39" s="26"/>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="H39" s="6">
+        <v>59</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="K39" s="6">
+        <v>1</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="25">
         <v>39</v>
       </c>
@@ -2473,8 +2672,20 @@
       </c>
       <c r="E40" s="26"/>
       <c r="F40" s="26"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="H40" s="15">
+        <v>66</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="K40" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="10">
         <v>40</v>
       </c>
@@ -2489,8 +2700,20 @@
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="H41" s="15">
+        <v>67</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="J41" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="K41" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="10">
         <v>41</v>
       </c>
@@ -2506,7 +2729,7 @@
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:13">
       <c r="A43" s="10">
         <v>42</v>
       </c>
@@ -2522,7 +2745,7 @@
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:13">
       <c r="A44" s="10">
         <v>43</v>
       </c>
@@ -2538,7 +2761,7 @@
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:13">
       <c r="A45" s="10">
         <v>44</v>
       </c>
@@ -2554,7 +2777,7 @@
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:13">
       <c r="A46" s="10">
         <v>45</v>
       </c>
@@ -2570,7 +2793,7 @@
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:13">
       <c r="A47" s="10">
         <v>46</v>
       </c>
@@ -2586,7 +2809,7 @@
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:13">
       <c r="A48" s="10">
         <v>47</v>
       </c>
